--- a/docs/設計書/データセットテンプレート_散布図プロット_設計書.xlsx
+++ b/docs/設計書/データセットテンプレート_散布図プロット_設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\rde2\gitlab\RDE_REGISTRATION_COMMON_SCATTERPLOT\docs\設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonokawa/gitlab/rde/catalog-templates-tmp/template_registration_common_scatterplot/docs/設計書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D59550-C99A-4E0C-A749-6AF9318C9056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CFFA8DE-496D-604F-8B6A-4F8448D00A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="説明" sheetId="20" r:id="rId1"/>
@@ -126,9 +126,20 @@
     <definedName name="膨張計">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1660,6 +1671,13 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>園川</t>
+    <rPh sb="0" eb="2">
+      <t>ソノカワ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>design_specifications</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1807,7 +1825,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="BIZ UDPゴシック"/>
-        <family val="3"/>
         <charset val="128"/>
       </rPr>
       <t>(自動入力)</t>
@@ -2842,16 +2859,12 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
-  <si>
-    <t>NIMS</t>
-    <phoneticPr fontId="3"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3086,6 +3099,12 @@
       <color theme="0"/>
       <name val="BIZ UDPゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="BIZ UDPゴシック"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3754,26 +3773,26 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3782,10 +3801,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -15967,10 +15986,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E6AC07-CCE9-0C4D-897D-5F665AAEF45F}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15979,29 +15998,29 @@
         <v>167</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C1" s="72" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="18">
       <c r="A2" s="70" t="s">
         <v>169</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C2" s="72" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" ht="18">
       <c r="A3" s="70" t="s">
         <v>170</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C3" s="72" t="s">
         <v>171</v>
@@ -16014,7 +16033,7 @@
       <c r="B4" s="72"/>
       <c r="C4" s="72"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" ht="18">
       <c r="A5" s="73"/>
     </row>
     <row r="6" spans="1:3">
@@ -16085,7 +16104,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D27A344-5008-4443-8A0C-671823B8F876}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -16094,90 +16113,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="111" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1" s="111" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B2" s="111" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C2" s="111" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B3" s="111" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C3" s="111" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="111" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B5" s="111" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" s="111" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="111" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" s="111" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" s="111" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="111" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C7" s="111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -16189,73 +16208,73 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894D1837-DEE1-C349-99B9-E814A8FD937E}">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.875" customWidth="1"/>
+    <col min="8" max="8" width="42.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.83203125" customWidth="1"/>
     <col min="13" max="13" width="41.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="111" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C1" s="111" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D1" s="98" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E1" s="98" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F1" s="98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G1" s="98" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1" s="98" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I1" s="98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J1" s="98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K1" s="98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L1" s="98" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M1" s="98" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="111" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B2" s="111" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C2" s="111" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D2" s="98" t="str">
         <f>VLOOKUP(A2,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16300,13 +16319,13 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B3" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C3" s="111" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D3" s="98" t="str">
         <f>VLOOKUP(A3,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16351,13 +16370,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B4" s="111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D4" s="98" t="str">
         <f>VLOOKUP(A4,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16402,13 +16421,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B5" s="111" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C5" s="111" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D5" s="98" t="str">
         <f>VLOOKUP(A5,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16453,13 +16472,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B6" s="111" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C6" s="111" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D6" s="98" t="str">
         <f>VLOOKUP(A6,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16504,13 +16523,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C7" s="111" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D7" s="98" t="str">
         <f>VLOOKUP(A7,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16555,13 +16574,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D8" s="98" t="str">
         <f>VLOOKUP(A8,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16606,13 +16625,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B9" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C9" s="111" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D9" s="98" t="str">
         <f>VLOOKUP(A9,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16657,13 +16676,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B10" s="111" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C10" s="111" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D10" s="98" t="str">
         <f>VLOOKUP(A10,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16708,13 +16727,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B11" s="111" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C11" s="111" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D11" s="98" t="str">
         <f>VLOOKUP(A11,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16759,13 +16778,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B12" s="111" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C12" s="111" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D12" s="98" t="str">
         <f>VLOOKUP(A12,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16810,13 +16829,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B13" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C13" s="111" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D13" s="98" t="str">
         <f>VLOOKUP(A13,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16861,13 +16880,13 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B14" s="111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C14" s="111" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D14" s="98" t="str">
         <f>VLOOKUP(A14,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16912,13 +16931,13 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B15" s="111" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C15" s="111" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D15" s="98" t="str">
         <f>VLOOKUP(A15,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -16963,13 +16982,13 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C16" s="111" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D16" s="98" t="str">
         <f>VLOOKUP(A16,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17014,13 +17033,13 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B17" s="111" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C17" s="111" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D17" s="98" t="str">
         <f>VLOOKUP(A17,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17065,13 +17084,13 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="111" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B18" s="111" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C18" s="111" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D18" s="98" t="str">
         <f>VLOOKUP(A18,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17116,13 +17135,13 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B19" s="111" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D19" s="98" t="str">
         <f>VLOOKUP(A19,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17167,13 +17186,13 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B20" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C20" s="111" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D20" s="98" t="str">
         <f>VLOOKUP(A20,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17218,13 +17237,13 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B21" s="111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C21" s="111" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D21" s="98" t="str">
         <f>VLOOKUP(A21,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17269,13 +17288,13 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B22" s="111" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C22" s="111" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D22" s="98" t="str">
         <f>VLOOKUP(A22,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17320,13 +17339,13 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B23" s="111" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C23" s="111" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D23" s="98" t="str">
         <f>VLOOKUP(A23,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17371,13 +17390,13 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="111" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B24" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C24" s="111" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D24" s="98" t="str">
         <f>VLOOKUP(A24,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17422,13 +17441,13 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="111" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B25" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C25" s="111" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D25" s="98" t="str">
         <f>VLOOKUP(A25,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17473,13 +17492,13 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B26" s="111" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C26" s="111" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D26" s="98" t="str">
         <f>VLOOKUP(A26,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17524,13 +17543,13 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B27" s="111" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C27" s="111" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D27" s="98" t="str">
         <f>VLOOKUP(A27,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17575,13 +17594,13 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B28" s="111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C28" s="111" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D28" s="98" t="str">
         <f>VLOOKUP(A28,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17626,13 +17645,13 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B29" s="111" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C29" s="111" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D29" s="98" t="str">
         <f>VLOOKUP(A29,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17677,13 +17696,13 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B30" s="111" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C30" s="111" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D30" s="98" t="str">
         <f>VLOOKUP(A30,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17728,13 +17747,13 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B31" s="111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C31" s="111" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D31" s="98" t="str">
         <f>VLOOKUP(A31,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17779,13 +17798,13 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B32" s="111" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C32" s="111" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D32" s="98" t="str">
         <f>VLOOKUP(A32,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17830,13 +17849,13 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B33" s="111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C33" s="111" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D33" s="98" t="str">
         <f>VLOOKUP(A33,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17881,13 +17900,13 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B34" s="111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C34" s="111" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D34" s="98" t="str">
         <f>VLOOKUP(A34,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17932,13 +17951,13 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B35" s="111" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C35" s="111" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D35" s="98" t="str">
         <f>VLOOKUP(A35,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -17983,13 +18002,13 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B36" s="111" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C36" s="111" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D36" s="98" t="str">
         <f>VLOOKUP(A36,sample.sample_class!A:C,2,FALSE)&amp;""</f>
@@ -18042,22 +18061,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A61A9FF-3E2A-4816-B225-73A91309AAFB}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N57"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="49.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.375" customWidth="1"/>
-    <col min="14" max="14" width="104.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.33203125" customWidth="1"/>
+    <col min="14" max="14" width="104.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -18100,7 +18119,7 @@
       </c>
       <c r="N1" s="18"/>
     </row>
-    <row r="2" spans="1:14" ht="98.25">
+    <row r="2" spans="1:14" ht="107">
       <c r="A2" s="18"/>
       <c r="B2" s="20" t="s">
         <v>13</v>
@@ -18326,7 +18345,7 @@
       <c r="M10" s="39"/>
       <c r="N10" s="26"/>
     </row>
-    <row r="11" spans="1:14" ht="28.5">
+    <row r="11" spans="1:14" ht="32">
       <c r="A11" s="44" t="s">
         <v>153</v>
       </c>
@@ -18702,7 +18721,7 @@
       <c r="M31" s="39"/>
       <c r="N31" s="26"/>
     </row>
-    <row r="32" spans="1:14" ht="28.5">
+    <row r="32" spans="1:14" ht="32">
       <c r="A32" s="44" t="s">
         <v>154</v>
       </c>
@@ -19064,7 +19083,7 @@
       <c r="M45" s="39"/>
       <c r="N45" s="26"/>
     </row>
-    <row r="46" spans="1:14" ht="27">
+    <row r="46" spans="1:14" ht="30">
       <c r="A46" s="48" t="s">
         <v>114</v>
       </c>
@@ -19423,36 +19442,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA4F778-CE81-A04E-A403-2BD85952C1F4}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:AC80"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="45" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="25.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="14" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="52" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="32.875" customWidth="1"/>
-    <col min="29" max="29" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="32.83203125" customWidth="1"/>
+    <col min="29" max="29" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -19651,13 +19670,13 @@
         <v>253</v>
       </c>
       <c r="C6" s="74" t="s">
+        <v>297</v>
+      </c>
+      <c r="D6" s="74" t="s">
         <v>296</v>
       </c>
-      <c r="D6" s="74" t="s">
-        <v>295</v>
-      </c>
       <c r="E6" s="74" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F6" s="74" t="s">
         <v>193</v>
@@ -19749,13 +19768,13 @@
       </c>
       <c r="E7" s="96"/>
       <c r="F7" s="99" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G7" s="99" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H7" s="97" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I7" s="97"/>
       <c r="J7" s="97"/>
@@ -19783,10 +19802,10 @@
       <c r="S7" s="97"/>
       <c r="T7" s="97"/>
       <c r="U7" s="97" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="V7" s="97" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="W7" s="97"/>
       <c r="X7" s="97"/>
@@ -19809,10 +19828,10 @@
       </c>
       <c r="E8" s="96"/>
       <c r="F8" s="99" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G8" s="99" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H8" s="97"/>
       <c r="I8" s="97"/>
@@ -19841,10 +19860,10 @@
       <c r="S8" s="97"/>
       <c r="T8" s="97"/>
       <c r="U8" s="97" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="V8" s="97" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="W8" s="97"/>
       <c r="X8" s="97"/>
@@ -19869,10 +19888,10 @@
       </c>
       <c r="E9" s="96"/>
       <c r="F9" s="99" t="s">
+        <v>515</v>
+      </c>
+      <c r="G9" s="99" t="s">
         <v>514</v>
-      </c>
-      <c r="G9" s="99" t="s">
-        <v>513</v>
       </c>
       <c r="H9" s="97"/>
       <c r="I9" s="97"/>
@@ -19901,10 +19920,10 @@
       <c r="S9" s="97"/>
       <c r="T9" s="97"/>
       <c r="U9" s="97" t="s">
+        <v>524</v>
+      </c>
+      <c r="V9" s="97" t="s">
         <v>523</v>
-      </c>
-      <c r="V9" s="97" t="s">
-        <v>522</v>
       </c>
       <c r="W9" s="97"/>
       <c r="X9" s="97"/>
@@ -19929,10 +19948,10 @@
       </c>
       <c r="E10" s="96"/>
       <c r="F10" s="99" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G10" s="99" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H10" s="102"/>
       <c r="I10" s="97"/>
@@ -19983,10 +20002,10 @@
       </c>
       <c r="E11" s="96"/>
       <c r="F11" s="99" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G11" s="99" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H11" s="102"/>
       <c r="I11" s="97"/>
@@ -20037,10 +20056,10 @@
       </c>
       <c r="E12" s="96"/>
       <c r="F12" s="99" t="s">
+        <v>465</v>
+      </c>
+      <c r="G12" s="99" t="s">
         <v>464</v>
-      </c>
-      <c r="G12" s="99" t="s">
-        <v>463</v>
       </c>
       <c r="H12" s="102"/>
       <c r="I12" s="97"/>
@@ -20091,10 +20110,10 @@
       </c>
       <c r="E13" s="96"/>
       <c r="F13" s="99" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G13" s="99" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H13" s="102"/>
       <c r="I13" s="97"/>
@@ -20145,10 +20164,10 @@
       </c>
       <c r="E14" s="96"/>
       <c r="F14" s="99" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G14" s="99" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H14" s="102"/>
       <c r="I14" s="97"/>
@@ -20199,10 +20218,10 @@
       </c>
       <c r="E15" s="96"/>
       <c r="F15" s="99" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G15" s="99" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H15" s="102"/>
       <c r="I15" s="97"/>
@@ -20253,10 +20272,10 @@
       </c>
       <c r="E16" s="96"/>
       <c r="F16" s="99" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G16" s="99" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H16" s="102"/>
       <c r="I16" s="97"/>
@@ -20307,10 +20326,10 @@
       </c>
       <c r="E17" s="96"/>
       <c r="F17" s="99" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G17" s="99" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H17" s="102"/>
       <c r="I17" s="97"/>
@@ -20361,10 +20380,10 @@
       </c>
       <c r="E18" s="96"/>
       <c r="F18" s="99" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G18" s="99" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H18" s="102"/>
       <c r="I18" s="97"/>
@@ -20415,10 +20434,10 @@
       </c>
       <c r="E19" s="96"/>
       <c r="F19" s="99" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G19" s="99" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H19" s="102"/>
       <c r="I19" s="97"/>
@@ -20469,10 +20488,10 @@
       </c>
       <c r="E20" s="96"/>
       <c r="F20" s="99" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G20" s="99" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H20" s="102"/>
       <c r="I20" s="97"/>
@@ -20523,10 +20542,10 @@
       </c>
       <c r="E21" s="96"/>
       <c r="F21" s="99" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G21" s="99" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H21" s="102"/>
       <c r="I21" s="97"/>
@@ -21172,7 +21191,7 @@
         <v>257</v>
       </c>
       <c r="C34" s="75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D34" s="108" t="s">
         <v>258</v>
@@ -23498,25 +23517,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED506E9B-BF5A-404C-A282-87283C03F050}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:R103"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="65.125" customWidth="1"/>
-    <col min="4" max="4" width="31.125" customWidth="1"/>
-    <col min="5" max="5" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.1640625" customWidth="1"/>
+    <col min="4" max="4" width="31.1640625" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="55.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.375" customWidth="1"/>
-    <col min="12" max="12" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.5" customWidth="1"/>
-    <col min="14" max="14" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.125" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" customWidth="1"/>
     <col min="16" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="17" width="49.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="49.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="68" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23579,10 +23598,10 @@
         <v>191</v>
       </c>
       <c r="B2" s="74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D2" s="74" t="s">
         <v>192</v>
@@ -23666,7 +23685,7 @@
         <v>206</v>
       </c>
       <c r="Q3" s="81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R3" s="103"/>
     </row>
@@ -23706,7 +23725,7 @@
         <v>206</v>
       </c>
       <c r="Q4" s="81" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R4" s="103"/>
     </row>
@@ -23746,7 +23765,7 @@
         <v>206</v>
       </c>
       <c r="Q5" s="81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="R5" s="103"/>
     </row>
@@ -23826,7 +23845,7 @@
         <v>206</v>
       </c>
       <c r="Q7" s="81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="R7" s="103"/>
     </row>
@@ -23866,7 +23885,7 @@
         <v>206</v>
       </c>
       <c r="Q8" s="81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R8" s="103"/>
     </row>
@@ -23906,7 +23925,7 @@
         <v>206</v>
       </c>
       <c r="Q9" s="81" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R9" s="103"/>
     </row>
@@ -23946,7 +23965,7 @@
         <v>206</v>
       </c>
       <c r="Q10" s="81" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="R10" s="103"/>
     </row>
@@ -24178,7 +24197,7 @@
         <v>206</v>
       </c>
       <c r="Q16" s="81" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="R16" s="103"/>
     </row>
@@ -24218,7 +24237,7 @@
         <v>206</v>
       </c>
       <c r="Q17" s="81" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R17" s="103"/>
     </row>
@@ -24248,7 +24267,7 @@
         <v/>
       </c>
       <c r="K18" s="80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L18" s="80"/>
       <c r="M18" s="80"/>
@@ -24260,7 +24279,7 @@
         <v>206</v>
       </c>
       <c r="Q18" s="81" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R18" s="103"/>
     </row>
@@ -24290,7 +24309,7 @@
         <v/>
       </c>
       <c r="K19" s="76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L19" s="80"/>
       <c r="M19" s="80"/>
@@ -24302,7 +24321,7 @@
         <v>206</v>
       </c>
       <c r="Q19" s="81" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R19" s="103"/>
     </row>
@@ -24332,7 +24351,7 @@
         <v/>
       </c>
       <c r="K20" s="76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L20" s="80"/>
       <c r="M20" s="80"/>
@@ -24344,7 +24363,7 @@
         <v>206</v>
       </c>
       <c r="Q20" s="81" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R20" s="103"/>
     </row>
@@ -24374,7 +24393,7 @@
         <v/>
       </c>
       <c r="K21" s="76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L21" s="80"/>
       <c r="M21" s="80"/>
@@ -24386,7 +24405,7 @@
         <v>206</v>
       </c>
       <c r="Q21" s="81" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R21" s="103"/>
     </row>
@@ -24426,7 +24445,7 @@
         <v>206</v>
       </c>
       <c r="Q22" s="81" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R22" s="103"/>
     </row>
@@ -24456,7 +24475,7 @@
         <v/>
       </c>
       <c r="K23" s="80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L23" s="80"/>
       <c r="M23" s="80"/>
@@ -24468,7 +24487,7 @@
         <v>206</v>
       </c>
       <c r="Q23" s="81" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R23" s="103"/>
     </row>
@@ -24498,7 +24517,7 @@
         <v/>
       </c>
       <c r="K24" s="80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L24" s="80"/>
       <c r="M24" s="80"/>
@@ -24510,7 +24529,7 @@
         <v>206</v>
       </c>
       <c r="Q24" s="81" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R24" s="103"/>
     </row>
@@ -24588,7 +24607,7 @@
         <v>206</v>
       </c>
       <c r="Q26" s="81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R26" s="103"/>
     </row>
@@ -24628,7 +24647,7 @@
         <v>206</v>
       </c>
       <c r="Q27" s="81" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="R27" s="103"/>
     </row>
@@ -27569,26 +27588,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B6AFBD-FF6B-F849-A1C8-90916185383A}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="5" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.625" customWidth="1"/>
-    <col min="8" max="9" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.625" customWidth="1"/>
+    <col min="3" max="5" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6640625" customWidth="1"/>
     <col min="17" max="19" width="29" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="22.5" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="15.5" hidden="1" customWidth="1"/>
     <col min="22" max="23" width="22" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="13" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="14.125" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="11.375" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="14.1640625" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -27853,10 +27872,10 @@
         <v>231</v>
       </c>
       <c r="B8" s="74" t="s">
+        <v>428</v>
+      </c>
+      <c r="C8" s="74" t="s">
         <v>427</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>426</v>
       </c>
       <c r="D8" s="74" t="s">
         <v>193</v>
@@ -27941,10 +27960,10 @@
         <v>dataset_title</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E9" s="94" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F9" s="80" t="s">
         <v>206</v>
@@ -27992,10 +28011,10 @@
         <v>abstract</v>
       </c>
       <c r="D10" s="94" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E10" s="94" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F10" s="80" t="s">
         <v>206</v>
@@ -28043,10 +28062,10 @@
         <v>data_creator</v>
       </c>
       <c r="D11" s="94" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E11" s="94" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F11" s="80" t="s">
         <v>206</v>
@@ -28094,10 +28113,10 @@
         <v>language</v>
       </c>
       <c r="D12" s="94" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E12" s="94" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F12" s="80" t="s">
         <v>206</v>
@@ -28145,10 +28164,10 @@
         <v>experimental_apparatus</v>
       </c>
       <c r="D13" s="94" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E13" s="94" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F13" s="80" t="s">
         <v>206</v>
@@ -28196,10 +28215,10 @@
         <v>data_distributio</v>
       </c>
       <c r="D14" s="94" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F14" s="80" t="s">
         <v>206</v>
@@ -28249,10 +28268,10 @@
         <v>raw_data_type</v>
       </c>
       <c r="D15" s="94" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E15" s="94" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F15" s="80" t="s">
         <v>206</v>
@@ -28300,16 +28319,16 @@
         <v>stored_data</v>
       </c>
       <c r="D16" s="94" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E16" s="94" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F16" s="80" t="s">
         <v>206</v>
       </c>
       <c r="G16" s="78" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H16" s="95" t="str">
         <f t="shared" si="3"/>
@@ -28350,16 +28369,16 @@
         <v>remarks</v>
       </c>
       <c r="D17" s="94" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E17" s="94" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F17" s="80" t="s">
         <v>206</v>
       </c>
       <c r="G17" s="78" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H17" s="95" t="str">
         <f t="shared" si="3"/>
@@ -28400,10 +28419,10 @@
         <v>references</v>
       </c>
       <c r="D18" s="94" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E18" s="94" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F18" s="80" t="s">
         <v>206</v>
@@ -28518,104 +28537,104 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A7BFD0-FE38-1048-880C-5BA5FA49C5F3}">
   <dimension ref="A2:B39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="45.625" style="117" customWidth="1"/>
-    <col min="2" max="2" width="87.875" style="112" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" style="117" customWidth="1"/>
+    <col min="2" max="2" width="87.83203125" style="112" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="18">
       <c r="A2" s="116" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B2" s="115"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="19">
       <c r="A3" s="120" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B3" s="121" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18">
       <c r="A4" s="122" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B4" s="123" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18">
       <c r="A5" s="122"/>
       <c r="B5" s="124" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18">
       <c r="A6" s="122"/>
       <c r="B6" s="125" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18">
       <c r="A7" s="122"/>
       <c r="B7" s="125" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="122"/>
       <c r="B8" s="123"/>
     </row>
-    <row r="9" spans="1:2" ht="37.5">
+    <row r="9" spans="1:2" ht="36">
       <c r="A9" s="122" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B9" s="123" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18">
       <c r="A10" s="122"/>
       <c r="B10" s="123" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="37.5">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="36">
       <c r="A11" s="122"/>
       <c r="B11" s="123" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="37.5">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="36">
       <c r="A12" s="122"/>
       <c r="B12" s="123" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="122"/>
       <c r="B13" s="123"/>
     </row>
-    <row r="14" spans="1:2" ht="37.5">
+    <row r="14" spans="1:2" ht="36">
       <c r="A14" s="122" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B14" s="123" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18">
       <c r="A15" s="122"/>
       <c r="B15" s="123" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18">
       <c r="A16" s="122"/>
       <c r="B16" s="123" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -28624,16 +28643,16 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="122" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B18" s="126" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="122"/>
       <c r="B19" s="126" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -28641,7 +28660,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="117" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -28697,22 +28716,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5BDA99-C1C0-4A93-80FB-46D5AFBA6B85}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="27.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.625" customWidth="1"/>
-    <col min="5" max="5" width="48.875" customWidth="1"/>
-    <col min="6" max="6" width="90.625" customWidth="1"/>
+    <col min="4" max="4" width="61.6640625" customWidth="1"/>
+    <col min="5" max="5" width="48.83203125" customWidth="1"/>
+    <col min="6" max="6" width="90.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="18">
       <c r="A1" s="64" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5">
+    <row r="2" spans="1:6" ht="18">
       <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
@@ -28725,48 +28744,48 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="37.5">
+    <row r="3" spans="1:6" ht="36">
       <c r="A3" s="53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B3" s="152" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C3" s="153"/>
       <c r="D3" s="154"/>
       <c r="E3" s="55" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18">
       <c r="A4" s="53"/>
       <c r="B4" s="152"/>
       <c r="C4" s="157"/>
       <c r="D4" s="158"/>
       <c r="E4" s="55"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="18">
       <c r="A5" s="53"/>
       <c r="B5" s="152"/>
       <c r="C5" s="157"/>
       <c r="D5" s="158"/>
       <c r="E5" s="55"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="18">
       <c r="A6" s="53"/>
       <c r="B6" s="152"/>
       <c r="C6" s="157"/>
       <c r="D6" s="158"/>
       <c r="E6" s="55"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="18">
       <c r="A7" s="53"/>
       <c r="B7" s="152"/>
       <c r="C7" s="157"/>
       <c r="D7" s="158"/>
       <c r="E7" s="55"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="18">
       <c r="A8" s="53"/>
       <c r="B8" s="61"/>
       <c r="C8" s="62"/>
@@ -28790,7 +28809,7 @@
       <c r="E10" s="65"/>
       <c r="F10" s="66"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="19">
       <c r="A11" s="67" t="s">
         <v>165</v>
       </c>
@@ -28805,78 +28824,78 @@
       </c>
       <c r="E11" s="69"/>
     </row>
-    <row r="12" spans="1:6" ht="37.5">
+    <row r="12" spans="1:6" ht="36">
       <c r="A12" s="53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E12" s="54"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="18">
       <c r="A13" s="53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E13" s="54"/>
     </row>
-    <row r="14" spans="1:6" ht="273.95" customHeight="1">
+    <row r="14" spans="1:6" ht="274" customHeight="1">
       <c r="A14" s="53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D14" s="113" t="s">
+        <v>463</v>
+      </c>
+      <c r="E14" s="54" t="s">
         <v>462</v>
       </c>
-      <c r="E14" s="54" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="53"/>
       <c r="B15" s="56"/>
       <c r="C15" s="57"/>
       <c r="D15" s="58"/>
       <c r="E15" s="54"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="18">
       <c r="A16" s="53"/>
       <c r="B16" s="59"/>
       <c r="C16" s="57"/>
       <c r="D16" s="60"/>
       <c r="E16" s="60"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" ht="18">
       <c r="A18" s="114" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="19">
       <c r="A19" s="67" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -28900,19 +28919,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{878915FE-5B0B-4DAA-9E76-98335F4D8B93}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:G59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="12"/>
-    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="63.625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="63.6640625" style="13" customWidth="1"/>
     <col min="7" max="7" width="64.5" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" s="1" customFormat="1" ht="17.25">
+    <row r="2" spans="2:7" s="1" customFormat="1">
       <c r="B2" s="1" t="s">
         <v>92</v>
       </c>
@@ -28922,11 +28941,11 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="3" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="4" spans="2:7" s="3" customFormat="1" ht="15">
       <c r="B4" s="5" t="s">
         <v>94</v>
       </c>
@@ -28943,394 +28962,394 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="5" spans="2:7" s="3" customFormat="1" ht="15">
       <c r="B5" s="7">
         <v>45450</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>524</v>
+        <v>269</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" s="3" customFormat="1" ht="13.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="7" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
     </row>
-    <row r="8" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="8" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="9"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="9" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="9"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="10" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="9"/>
       <c r="F10" s="11"/>
     </row>
-    <row r="11" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="11" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="9"/>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="12" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="9"/>
       <c r="F12" s="11"/>
     </row>
-    <row r="13" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="13" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="9"/>
       <c r="F13" s="11"/>
     </row>
-    <row r="14" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="14" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="9"/>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="15" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B15" s="10"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="2:7" s="3" customFormat="1" ht="13.5">
+    <row r="16" spans="2:7" s="3" customFormat="1" ht="14">
       <c r="B16" s="10"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="17" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="18" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B18" s="7"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="19" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="20" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="21" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="22" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B22" s="10"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="23" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B23" s="10"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="24" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B24" s="10"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="25" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B25" s="10"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="26" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B26" s="10"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="27" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B27" s="10"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="28" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B28" s="10"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="29" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B29" s="10"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="30" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B30" s="10"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="31" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B31" s="10"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="32" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B32" s="10"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="33" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B33" s="10"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="34" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B34" s="10"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="35" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B35" s="10"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="36" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B36" s="10"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="37" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B37" s="10"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="38" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B38" s="10"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="39" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B39" s="10"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="40" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B40" s="10"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="41" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B41" s="10"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="42" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B42" s="10"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="43" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B43" s="10"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="44" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B44" s="10"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="45" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B45" s="10"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="46" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B46" s="10"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="47" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B47" s="10"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
     </row>
-    <row r="48" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="48" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B48" s="10"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="49" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B49" s="10"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
     </row>
-    <row r="50" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="50" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B50" s="10"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="51" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B51" s="10"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
     </row>
-    <row r="52" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="52" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B52" s="10"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
     </row>
-    <row r="53" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="53" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B53" s="10"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
     </row>
-    <row r="54" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="54" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B54" s="10"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
-    <row r="55" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="55" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B55" s="10"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
     </row>
-    <row r="56" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="56" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B56" s="10"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
     </row>
-    <row r="57" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="57" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
     </row>
-    <row r="58" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="58" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
     </row>
-    <row r="59" spans="2:6" s="3" customFormat="1" ht="13.5">
+    <row r="59" spans="2:6" s="3" customFormat="1" ht="14">
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -29347,50 +29366,50 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3695370-B12E-0047-A82B-92E4AC317AEF}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="40.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.375" customWidth="1"/>
-    <col min="8" max="8" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.33203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="111" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C1" s="98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D1" s="98" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="98" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F1" s="98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G1" s="98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1" s="98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="111" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B2" s="111" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C2" s="98" t="str">
         <f>VLOOKUP(A2,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29419,10 +29438,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B3" s="111" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C3" s="98" t="str">
         <f>VLOOKUP(A3,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29451,10 +29470,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="111" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B4" s="111" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C4" s="98" t="str">
         <f>VLOOKUP(A4,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29483,10 +29502,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B5" s="111" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C5" s="98" t="str">
         <f>VLOOKUP(A5,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29515,10 +29534,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="111" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B6" s="111" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C6" s="98" t="str">
         <f>VLOOKUP(A6,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29547,10 +29566,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="111" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C7" s="98" t="str">
         <f>VLOOKUP(A7,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29579,10 +29598,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C8" s="98" t="str">
         <f>VLOOKUP(A8,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29611,10 +29630,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="111" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B9" s="111" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C9" s="98" t="str">
         <f>VLOOKUP(A9,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29643,10 +29662,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="111" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" s="111" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C10" s="98" t="str">
         <f>VLOOKUP(A10,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29675,10 +29694,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="111" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B11" s="111" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C11" s="98" t="str">
         <f>VLOOKUP(A11,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29707,10 +29726,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B12" s="111" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C12" s="98" t="str">
         <f>VLOOKUP(A12,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29739,10 +29758,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="111" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B13" s="111" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C13" s="98" t="str">
         <f>VLOOKUP(A13,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29771,10 +29790,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="111" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B14" s="111" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C14" s="98" t="str">
         <f>VLOOKUP(A14,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29803,10 +29822,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="111" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B15" s="111" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C15" s="98" t="str">
         <f>VLOOKUP(A15,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29835,10 +29854,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="111" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C16" s="98" t="str">
         <f>VLOOKUP(A16,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29867,10 +29886,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="111" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" s="111" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C17" s="98" t="str">
         <f>VLOOKUP(A17,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29899,10 +29918,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B18" s="111" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C18" s="98" t="str">
         <f>VLOOKUP(A18,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29931,10 +29950,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="111" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B19" s="111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C19" s="98" t="str">
         <f>VLOOKUP(A19,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29963,10 +29982,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B20" s="111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C20" s="98" t="str">
         <f>VLOOKUP(A20,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -29995,10 +30014,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B21" s="111" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C21" s="98" t="str">
         <f>VLOOKUP(A21,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -30027,10 +30046,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B22" s="111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C22" s="98" t="str">
         <f>VLOOKUP(A22,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -30059,10 +30078,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="111" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B23" s="111" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C23" s="98" t="str">
         <f>VLOOKUP(A23,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -30091,10 +30110,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B24" s="111" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C24" s="98" t="str">
         <f>VLOOKUP(A24,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -30123,10 +30142,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B25" s="111" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C25" s="98" t="str">
         <f>VLOOKUP(A25,[5]dict.term!A:G,2,FALSE)&amp;""</f>
@@ -30171,15 +30190,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010051C3DC589983724E98472DFCE83CFE28" ma:contentTypeVersion="8" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="56ec90460d2d98ba0f9df34f0ad90fe5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fcac4235-3712-4f1a-9a68-cd81b1c94fd2" xmlns:ns3="03d23630-19bc-4208-bade-29ad47d0e872" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="64cd019f2d5f0eccec25873ecd453d84" ns2:_="" ns3:_="">
     <xsd:import namespace="fcac4235-3712-4f1a-9a68-cd81b1c94fd2"/>
@@ -30356,6 +30366,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
   <ds:schemaRefs>
@@ -30368,14 +30387,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1080EF-91B6-417D-A249-69224D257C51}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBBD398B-EE48-4CBF-8E35-C1D89BC3BAE8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30392,4 +30403,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1080EF-91B6-417D-A249-69224D257C51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>